--- a/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Plancha Grill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Línea Montaje" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Freidora" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plancha Grill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Línea Montaje" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freidora" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Plancha Grill'!$A$1:$G$26</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Línea Montaje'!$A$1:$G$25</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Freidora'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Plancha Grill'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Línea Montaje'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidora'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +80,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -138,44 +143,60 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -535,15 +556,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -551,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -558,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -579,6 +603,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -586,8 +611,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -601,16 +651,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Estación de Plancha / Grill — Smash &amp; Classic Burgers</t>
@@ -624,10 +674,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -652,7 +703,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -669,10 +720,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -698,10 +747,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -727,10 +774,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -756,10 +801,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -785,10 +828,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -821,10 +862,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -850,10 +889,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -879,10 +916,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -908,10 +943,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -937,10 +970,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -966,10 +997,8 @@
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1002,10 +1031,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1031,10 +1058,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -1059,6 +1084,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -1067,14 +1093,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -1082,6 +1113,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -1099,7 +1131,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1114,16 +1156,16 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Línea de Montaje — Pan, Toppings y Salsas</t>
@@ -1137,10 +1179,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1165,7 +1208,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1182,10 +1225,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1211,10 +1252,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1240,10 +1279,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1269,10 +1306,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1298,10 +1333,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1334,10 +1367,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1363,10 +1394,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1392,10 +1421,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1421,10 +1448,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1457,10 +1482,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="19" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1486,10 +1509,8 @@
       <c r="G17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1515,10 +1536,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -1543,6 +1562,7 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="C21" s="15" t="inlineStr">
         <is>
@@ -1551,14 +1571,19 @@
       </c>
       <c r="D21" s="16">
         <f>COUNTIF(F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>de 12</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F21">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
@@ -1566,6 +1591,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
@@ -1583,7 +1609,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
@@ -1598,16 +1634,16 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Estación de Freidora — Patatas y Sides</t>
@@ -1621,10 +1657,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1649,7 +1686,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1666,10 +1703,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
@@ -1695,10 +1730,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -1724,10 +1757,8 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -1753,10 +1784,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
@@ -1782,10 +1811,8 @@
       <c r="G9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
@@ -1818,10 +1845,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -1847,10 +1872,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
@@ -1876,10 +1899,8 @@
       <c r="G13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -1905,10 +1926,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="19" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -1934,10 +1953,8 @@
       <c r="G15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="18" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -1970,10 +1987,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="18" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
@@ -1999,10 +2014,8 @@
       <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="19" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
@@ -2028,10 +2041,8 @@
       <c r="G19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
@@ -2056,6 +2067,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="C22" s="15" t="inlineStr">
         <is>
@@ -2064,14 +2076,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>de 13</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F22">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -2079,6 +2096,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
@@ -2096,7 +2114,17 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
@@ -13,8 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freidora" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Plancha Grill'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Plancha Grill'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Línea Montaje'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Línea Montaje'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Freidora'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidora'!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -646,7 +649,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1141,8 +1144,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1151,7 +1162,7 @@
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1619,8 +1630,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1629,7 +1648,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2124,7 +2143,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-hamburgueseria/02-partidas-cocina.xlsx
@@ -13,12 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freidora" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Plancha Grill'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Plancha Grill'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Plancha Grill'!$A$1:$G$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Línea Montaje'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Línea Montaje'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Línea Montaje'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Freidora'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidora'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Freidora'!$A$1:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +90,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +136,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -148,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +204,49 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,72 +624,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Línea de Producción de Burgers — Hamburguesería</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists para cada estación de la línea.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Plancha/Grill: cocción de patties y bacon</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• Línea de montaje: pan, queso, toppings, salsas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• Freidora: patatas, aros, nuggets</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = pendiente · ✓ = completada</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>▸ Estás en 02-partidas-cocina.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hamburgueseria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -651,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -701,7 +857,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -716,431 +872,523 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Precalentar plancha a 200-230°C</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Precalentar plancha a 200-230 °C</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de patties/carne picada</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Cámara</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Preparar prensa de smash si aplica</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Preparar bacon en plancha o pre-cocinar</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Verificar espátulas, prensas, termómetro</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Separar el utillaje de crudo: tabla, pinzas y espátula de la carne cruda marcadas y distintas de las del pan y los toppings</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Cocinero plancha</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Smash burger: bola 80-100g → prensar en plancha caliente</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Controlar punto de carne: medio, hecho, muy hecho</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Controlar el punto con termómetro de sonda: la carne PICADA necesita 70 °C en el CENTRO (75 °C si la sirves a niños, embarazadas o personas mayores) — al picarla, lo de fuera pasa a estar dentro</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Fundir queso: tapar con campana 30s</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Tostar pan en plancha (corte hacia abajo, 20-30s)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Mantener plancha limpia entre tandas (rasqueta)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Comunicar al montaje: burger lista para montar</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Limpiar plancha a fondo con rasqueta y desengrasante</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Limpiar prensa y espátulas</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>Cocinero plancha</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="16">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F18 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1164,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1214,7 +1462,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1229,404 +1477,496 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Montar inserts: lechuga, tomate, cebolla, pepinillos</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Montar inserts: lechuga, tomate, cebolla y pepinillos — los de consumo crudo (lechuga, tomate, cebolla) se lavan y desinfectan con lejía apta para uso alimentario a la dosis del fabricante (habitual: 70 ppm, 5 min) y se ACLARAN con agua potable abundante</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Preparar salsas en biberones: burger sauce, BBQ, mayo, mostaza</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Cortar quesos en lonchas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Verificar stock de pan (brioche, pretzel, sesamo)</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Preparar extras: huevo frito, jalapeños, aros cebolla crispy</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Montar burger según comanda: base pan → salsa → patty → queso → toppings → tapa</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Pinchar con palillo/flag si es burger alta</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Reponer inserts cuando bajen</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Empaquetar para take-away/delivery (envolver en papel, caja)</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS</t>
         </is>
       </c>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Cubrir y refrigerar todos los inserts</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Limpiar línea completa</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Anotar las mermas del turno (producto, cantidad y motivo): inserts que no se pueden guardar, lonchas de queso rotas, pan aplastado y burgers mal montadas</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Cocinero línea</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Anotar consumos</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Cocinero línea</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
     <row r="21">
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D21" s="16">
-        <f>COUNTIF(F5:F19,"✓")</f>
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="16">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F21">
-        <f>COUNTIF(B5:B19,"?*")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="F27">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G19">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1650,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1700,7 +2040,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1715,431 +2055,496 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ANTES DEL SERVICIO</t>
         </is>
       </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Verificar nivel y calidad del aceite (test polares)</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Encender freidora y precalentar (175-180°C)</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Encender freidora y precalentar (175-180 °C)</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="F7" s="28" t="n"/>
+      <c r="G7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Preparar patatas: cortar frescas o sacar congeladas</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Preparar rebozados: aros de cebolla, jalapeño poppers</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Preparar nuggets/tenders de pollo si aplica</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Freír patatas por tandas (no sobrecargar cesta)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Controlar tiempo: patatas 3-4 min, aros 2-3 min</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Salar y condimentar al sacar</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Emplatar en cesta/cucurucho según presentación</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Mantener zona limpia de salpicaduras</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  DESPUÉS</t>
         </is>
       </c>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Apagar freidora y dejar enfriar</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Filtrar aceite o cambiar si está oscuro/huele</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Filtrar el aceite o cambiarlo si está oscuro o huele — SOLO por debajo de 40 °C, nunca en caliente</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Limpiar exterior de freidora</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Cocinero freidora</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="28" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="n"/>
+    </row>
     <row r="22">
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="28" t="n"/>
+      <c r="G25" s="28" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="16">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22">
-        <f>COUNTIF(B5:B20,"?*")</f>
+      <c r="F27">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
         <v>13.0</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Hamburguesería · AI Chef Pro · aichef.pro —</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Hamburguesería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="8">
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
